--- a/Packages/cn.etetet.crawlers/Luban/Config/Datas/CrawlerCardEffect.xlsx
+++ b/Packages/cn.etetet.crawlers/Luban/Config/Datas/CrawlerCardEffect.xlsx
@@ -15,12 +15,12 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>##var</t>
   </si>
@@ -154,7 +154,7 @@
     <t>GainMana</t>
   </si>
   <si>
-    <t>聚灵雨补灵力</t>
+    <t>聚灵雨不回灵力</t>
   </si>
   <si>
     <t>100401</t>
@@ -203,7 +203,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+  <numFmts count="0"/>
+  <fonts count="18">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -356,13 +357,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -413,19 +407,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.7999816888943144"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.5999938962981048"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.3999755851924192"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -436,19 +430,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.5999938962981048"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.3999755851924192"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -459,19 +453,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
+        <fgColor theme="6" tint="0.7999816888943144"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.5999938962981048"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.3999755851924192"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -482,19 +476,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
+        <fgColor theme="7" tint="0.7999816888943144"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.5999938962981048"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.3999755851924192"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -505,19 +499,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
+        <fgColor theme="8" tint="0.7999816888943144"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.5999938962981048"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.3999755851924192"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -528,19 +522,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor theme="9" tint="0.7999816888943144"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.5999938962981048"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.3999755851924192"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -576,7 +570,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.3999755851924192"/>
       </bottom>
       <diagonal/>
     </border>
@@ -662,181 +656,181 @@
     </border>
   </borders>
   <cellStyleXfs count="42">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="2" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="3" applyFont="1" fillId="0" applyFill="0" borderId="1" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="4" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="0" applyFill="0" borderId="9" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="6" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="7" applyFill="1" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="0" applyFill="0" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="4" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="6" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="5" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="0" fillId="8" applyFill="1" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - 着色 1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="标题" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="标题 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="标题 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="标题 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="标题 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="差" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 1" xfId="1" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 2" xfId="2" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 3" xfId="3" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 4" xfId="4" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 5" xfId="5" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 6" xfId="6" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 1" xfId="7" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 2" xfId="8" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 3" xfId="9" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 4" xfId="10" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 5" xfId="11" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 6" xfId="12" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 1" xfId="13" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 2" xfId="14" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 3" xfId="15" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 4" xfId="16" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 5" xfId="17" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 6" xfId="18" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="标题" xfId="19" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="标题 1" xfId="20" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="标题 2" xfId="21" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="标题 4" xfId="23" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="差" xfId="24" builtinId="27" customBuiltin="1"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="汇总" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="计算" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="检查单元格" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="解释性文本" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="警告文本" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="链接单元格" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="适中" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="输出" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="输入" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="着色 1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="着色 2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="着色 3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="着色 4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="着色 5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="着色 6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="注释" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="好" xfId="25" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="汇总" xfId="26" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="计算" xfId="27" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="检查单元格" xfId="28" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="解释性文本" xfId="29" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="警告文本" xfId="30" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="链接单元格" xfId="31" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="适中" xfId="32" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="输出" xfId="33" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="输入" xfId="34" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="着色 1" xfId="35" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="着色 2" xfId="36" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="着色 3" xfId="37" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="着色 4" xfId="38" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="着色 5" xfId="39" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="着色 6" xfId="40" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="注释" xfId="41" builtinId="10" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1171,304 +1165,310 @@
   <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="5" max="5" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" bestFit="1" width="17.83203125" customWidth="1"/>
+    <col min="7" max="7" bestFit="1" width="18.1640625" customWidth="1"/>
+    <col min="8" max="8" bestFit="1" width="15.6640625" customWidth="1"/>
+    <col min="9" max="9" bestFit="1" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="0" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="0" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
+    <row r="3">
+      <c r="A3" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="0" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
+    <row r="4">
+      <c r="A4" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="0" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
+    <row r="5">
+      <c r="A5" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="0" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
+    <row r="6">
+      <c r="A6" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="0" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
+    <row r="7">
+      <c r="A7" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="0">
+        <v>0</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="0" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="G7" t="s">
+      <c r="E8" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="0" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="0" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H10" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="I7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10" t="s">
-        <v>39</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="I10" s="0" t="s">
         <v>58</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>